--- a/coreweave/docs/reports/20261009_coreweave_v4.8_Tokenomics_v5.31.xlsx
+++ b/coreweave/docs/reports/20261009_coreweave_v4.8_Tokenomics_v5.31.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1978" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1980" uniqueCount="324">
   <si>
     <r>
       <rPr>
@@ -111,10 +111,20 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF555555"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收入口徑（</t>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">k </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">隨錨重算（價格不變，</t>
     </r>
     <r>
       <rPr>
@@ -133,7 +143,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">、隨需比例）不動；</t>
+      <t xml:space="preserve">＝證據價格 </t>
     </r>
     <r>
       <rPr>
@@ -143,7 +153,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">MW </t>
+      <t xml:space="preserve">÷ v5.31 </t>
     </r>
     <r>
       <rPr>
@@ -152,7 +162,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">口徑查證後維持 </t>
+      <t xml:space="preserve">同世代成本）；</t>
     </r>
     <r>
       <rPr>
@@ -162,7 +172,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">IT</t>
+      <t xml:space="preserve">2023 </t>
     </r>
     <r>
       <rPr>
@@ -171,7 +181,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">（</t>
+      <t xml:space="preserve">年底 </t>
     </r>
     <r>
       <rPr>
@@ -181,7 +191,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">10-K</t>
+      <t xml:space="preserve">MW </t>
     </r>
     <r>
       <rPr>
@@ -190,7 +200,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">、</t>
+      <t xml:space="preserve">依 </t>
     </r>
     <r>
       <rPr>
@@ -200,6 +210,101 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">10-K </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">原文 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">70</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MW </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">口徑查證後維持 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10-K</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">10-Q </t>
     </r>
     <r>
@@ -14637,6 +14742,37 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">0.82</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">k_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">長約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">0.89</t>
     </r>
     <r>
@@ -14677,6 +14813,46 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">1.04</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（三筆長約中位數）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">k_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">長約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">1.00</t>
     </r>
   </si>
@@ -14685,6 +14861,37 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">k_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">長約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.17</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -14766,6 +14973,74 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">10%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">k_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">現貨 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.83</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">隨需占比 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">20%</t>
     </r>
     <r>
@@ -14824,6 +15099,74 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">隨需占比 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">k_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">現貨 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.83</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">既有合約 </t>
     </r>
     <r>
@@ -15061,7 +15404,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">× 1.02</t>
+      <t xml:space="preserve">× 1.03</t>
     </r>
     <r>
       <rPr>
@@ -15317,6 +15660,84 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">(b) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">實際數更新：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2023 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年底主動電力 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100 → 70 MW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10-K FY2025 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">原文）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">① (c) GB300 </t>
     </r>
     <r>
@@ -15376,16 +15797,16 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">② (c) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收入錨：</t>
+      <t xml:space="preserve">②a (c) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收入錨下降：</t>
     </r>
     <r>
       <rPr>
@@ -15461,7 +15882,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">；含機架價格與維護費率；</t>
+      <t xml:space="preserve">），</t>
     </r>
     <r>
       <rPr>
@@ -15480,7 +15901,66 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">輸入不動）</t>
+      <t xml:space="preserve">維持 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v4.7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">數字</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">②b (c) k </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">隨錨重算（證據價格 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ v5.31 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同世代成本；價格不變）</t>
     </r>
   </si>
   <si>
@@ -15684,7 +16164,45 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">實際數更新</t>
+      <t xml:space="preserve">實際數更新（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2023 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年底 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
     </r>
   </si>
   <si>
@@ -15705,7 +16223,45 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">假設變更（①＋②）</t>
+      <t xml:space="preserve">假設變更（①＋②</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋②</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
     </r>
   </si>
   <si>
@@ -15780,15 +16336,15 @@
     <font>
       <sz val="9"/>
       <color rgb="FF555555"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF555555"/>
-      <name val="Cambria"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -16207,11 +16763,11 @@
         <v>18.4389160784888</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>29.3181542946211</v>
+        <v>42.7024438874061</v>
       </c>
       <c r="D5" s="5" t="n">
         <f aca="false">C5-B5</f>
-        <v>10.8792382161324</v>
+        <v>24.2635278089173</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>12</v>
@@ -16223,11 +16779,11 @@
         <v>51.013578305205</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>40.6837030341992</v>
+        <v>32.1474767393228</v>
       </c>
       <c r="I5" s="5" t="n">
         <f aca="false">H5-G5</f>
-        <v>-10.3298752710058</v>
+        <v>-18.8661015658822</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16238,11 +16794,11 @@
         <v>13.2946559274427</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>18.5333004436762</v>
+        <v>31.9865189051237</v>
       </c>
       <c r="D6" s="5" t="n">
         <f aca="false">C6-B6</f>
-        <v>5.23864451623355</v>
+        <v>18.6918629776811</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>12</v>
@@ -16254,11 +16810,11 @@
         <v>100.928227629337</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>89.4072913196021</v>
+        <v>79.3186736969194</v>
       </c>
       <c r="I6" s="5" t="n">
         <f aca="false">H6-G6</f>
-        <v>-11.5209363097349</v>
+        <v>-21.6095539324177</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16269,11 +16825,11 @@
         <v>0</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0</v>
+        <v>14.7158090153289</v>
       </c>
       <c r="D7" s="5" t="n">
         <f aca="false">C7-B7</f>
-        <v>0</v>
+        <v>14.7158090153289</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>12</v>
@@ -16285,11 +16841,11 @@
         <v>179.634002446844</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>165.385125098764</v>
+        <v>151.832159599564</v>
       </c>
       <c r="I7" s="5" t="n">
         <f aca="false">H7-G7</f>
-        <v>-14.2488773480801</v>
+        <v>-27.8018428472794</v>
       </c>
     </row>
   </sheetData>
@@ -16379,19 +16935,19 @@
         <v>25</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>8.11382745599041</v>
+        <v>8.23237923794364</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>8.25049212401025</v>
+        <v>8.72599068555684</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>8.33605601305693</v>
+        <v>8.96991524215975</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>8.29750080662351</v>
+        <v>8.97413701432632</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>7.97619709698908</v>
+        <v>8.67774827716783</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16483,19 +17039,19 @@
         <v>25</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>0.184804918429672</v>
+        <v>0.172486912161015</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>0.216090700452404</v>
+        <v>0.21192248620998</v>
       </c>
       <c r="F9" s="8" t="n">
         <v>0.277800866866406</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>0.408498600664463</v>
+        <v>0.410888755639463</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>0.578349703812881</v>
+        <v>0.58062604188431</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16596,10 +17152,10 @@
         <v>0.159859583348507</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>0.164349266263088</v>
+        <v>0.164160338675588</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>0.167631414583893</v>
+        <v>0.167451483548179</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16639,19 +17195,19 @@
         <v>25</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>0.447442135437141</v>
+        <v>0.453979748267183</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>0.454978594799789</v>
+        <v>0.481200263048183</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0.459697069457896</v>
+        <v>0.494651636655023</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>0.45757091826817</v>
+        <v>0.494884448945373</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>0.439852422435903</v>
+        <v>0.478539904993333</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16743,19 +17299,19 @@
         <v>25</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>3.37375956688314</v>
+        <v>3.36797917344453</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>3.41253026860668</v>
+        <v>3.43458372261265</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>3.20869260709684</v>
+        <v>3.24364717429397</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>3.18393678519572</v>
+        <v>3.22345154326042</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>3.18354659577773</v>
+        <v>3.22433048537088</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16795,19 +17351,19 @@
         <v>25</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>4.74006788910727</v>
+        <v>4.86440006449912</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>4.83796185540358</v>
+        <v>5.29140696294419</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>5.12736340596009</v>
+        <v>5.72626806786578</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>5.11356402142779</v>
+        <v>5.75068547106589</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>4.79265050121135</v>
+        <v>5.45341779179695</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16899,19 +17455,19 @@
         <v>25</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>2.78441054587726</v>
+        <v>2.77856644568533</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>2.70694952607254</v>
+        <v>2.65797937798749</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>1.94862628612165</v>
+        <v>1.96218463151598</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>1.60878685956648</v>
+        <v>1.62048093246909</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>1.47566772830576</v>
+        <v>1.48680494059396</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16951,19 +17507,19 @@
         <v>25</v>
       </c>
       <c r="D27" s="8" t="n">
-        <v>-3.63304912443169</v>
+        <v>-3.5028728488479</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>-3.5293653073693</v>
+        <v>-3.02695005174364</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-2.31392739851905</v>
+        <v>-1.72858108200768</v>
       </c>
       <c r="G27" s="8" t="n">
-        <v>-1.90215288022203</v>
+        <v>-1.27672550348653</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>-2.02637225764997</v>
+        <v>-1.37674217935256</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17055,19 +17611,19 @@
         <v>25</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.584196288966891</v>
+        <v>0.590886294703084</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>0.586384640174897</v>
+        <v>0.606396127800419</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>0.615082647948742</v>
+        <v>0.638385972807367</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>0.616277616670536</v>
+        <v>0.640806515644401</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0.600869116313652</v>
+        <v>0.628436965168203</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17107,19 +17663,19 @@
         <v>25</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>8.11382745599041</v>
+        <v>8.23237923794364</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>8.25049212401025</v>
+        <v>8.72599068555684</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>8.31027025361177</v>
+        <v>8.96023240021956</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>8.17227358845674</v>
+        <v>8.89172210761935</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>7.67952920803828</v>
+        <v>8.45429809292861</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17211,19 +17767,19 @@
         <v>25</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>0.184804918429672</v>
+        <v>0.172486912161015</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>0.216090700452404</v>
+        <v>0.21192248620998</v>
       </c>
       <c r="F37" s="8" t="n">
         <v>0.275269342729324</v>
       </c>
       <c r="G37" s="8" t="n">
-        <v>0.388447069694966</v>
+        <v>0.390619937854057</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>0.503269330002712</v>
+        <v>0.505107910752712</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17324,10 +17880,10 @@
         <v>0.160650348887986</v>
       </c>
       <c r="G41" s="8" t="n">
-        <v>0.16649312933008</v>
+        <v>0.166321376977807</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>0.171535327163914</v>
+        <v>0.171389998250452</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17367,19 +17923,19 @@
         <v>25</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>0.447442135437141</v>
+        <v>0.453979748267183</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>0.454978594799789</v>
+        <v>0.481200263048183</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>0.458275097480727</v>
+        <v>0.4941176702257</v>
       </c>
       <c r="G43" s="8" t="n">
-        <v>0.450665184295479</v>
+        <v>0.49033962690561</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>0.423492484482111</v>
+        <v>0.466217603571209</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17471,19 +18027,19 @@
         <v>25</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>3.37375956688314</v>
+        <v>3.36797917344453</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>3.41253026860668</v>
+        <v>3.43458372261265</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>3.2230486591571</v>
+        <v>3.25889123190207</v>
       </c>
       <c r="G47" s="8" t="n">
-        <v>3.16769156513871</v>
+        <v>3.20936712355566</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>3.09424561502152</v>
+        <v>3.13866398594715</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17523,19 +18079,19 @@
         <v>25</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>4.74006788910727</v>
+        <v>4.86440006449912</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>4.83796185540358</v>
+        <v>5.29140696294419</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>5.08722159445467</v>
+        <v>5.70134116831749</v>
       </c>
       <c r="G49" s="8" t="n">
-        <v>5.00458202331804</v>
+        <v>5.68235498406369</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>4.58528359301676</v>
+        <v>5.31563410698146</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17627,19 +18183,19 @@
         <v>25</v>
       </c>
       <c r="D53" s="8" t="n">
-        <v>2.78441054587726</v>
+        <v>2.77856644568533</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>2.79679244903757</v>
+        <v>2.74782230095253</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>2.30948930846388</v>
+        <v>2.11019847162462</v>
       </c>
       <c r="G53" s="8" t="n">
-        <v>2.0865495907093</v>
+        <v>1.77328374161141</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>2.00046589624144</v>
+        <v>1.78806620011241</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17679,19 +18235,19 @@
         <v>25</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>-3.63304912443169</v>
+        <v>-3.5028728488479</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>-3.70149190575521</v>
+        <v>-3.19907665012955</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>-2.91316622152095</v>
+        <v>-2.09975581081887</v>
       </c>
       <c r="G55" s="8" t="n">
-        <v>-2.85873939504278</v>
+        <v>-1.86770058519924</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>-3.20372635354519</v>
+        <v>-2.26097614345146</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17783,19 +18339,19 @@
         <v>25</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.584196288966891</v>
+        <v>0.590886294703084</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>0.586384640174897</v>
+        <v>0.606396127800419</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>0.612160788903789</v>
+        <v>0.636293894361242</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>0.612385521501258</v>
+        <v>0.639061243175207</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>0.597078736052892</v>
+        <v>0.628749311717266</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17835,19 +18391,19 @@
         <v>25</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>8.11382745599041</v>
+        <v>8.23237923794364</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>8.25049212401025</v>
+        <v>8.72599068555684</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>8.2403744073878</v>
+        <v>8.93412416864912</v>
       </c>
       <c r="G61" s="8" t="n">
-        <v>7.92870344487834</v>
+        <v>8.73256667200274</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>7.33712416747983</v>
+        <v>8.19832038571227</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17939,19 +18495,19 @@
         <v>25</v>
       </c>
       <c r="D65" s="8" t="n">
-        <v>0.184804918429672</v>
+        <v>0.172486912161015</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>0.216090700452404</v>
+        <v>0.21192248620998</v>
       </c>
       <c r="F65" s="8" t="n">
         <v>0.268463816802364</v>
       </c>
       <c r="G65" s="8" t="n">
-        <v>0.349815679753734</v>
+        <v>0.35156992193722</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>0.417268174547427</v>
+        <v>0.41860532418379</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18052,10 +18608,10 @@
         <v>0.162776173130481</v>
       </c>
       <c r="G69" s="8" t="n">
-        <v>0.170623507716028</v>
+        <v>0.170484845266486</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>0.176007081573755</v>
+        <v>0.175901387818511</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18095,19 +18651,19 @@
         <v>25</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>0.447442135437141</v>
+        <v>0.453979748267183</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>0.454978594799789</v>
+        <v>0.481200263048183</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>0.454420646931677</v>
+        <v>0.49267791531968</v>
       </c>
       <c r="G71" s="8" t="n">
-        <v>0.437233355018534</v>
+        <v>0.481562899970637</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>0.404610342439664</v>
+        <v>0.452101551367433</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18199,19 +18755,19 @@
         <v>25</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>3.37375956688314</v>
+        <v>3.36797917344453</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>3.41253026860668</v>
+        <v>3.43458372261265</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>3.26161045504634</v>
+        <v>3.29986772343434</v>
       </c>
       <c r="G75" s="8" t="n">
-        <v>3.12479834065343</v>
+        <v>3.17074346533948</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>2.95915010205735</v>
+        <v>3.00787276686624</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18251,19 +18807,19 @@
         <v>25</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>4.74006788910727</v>
+        <v>4.86440006449912</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>4.83796185540358</v>
+        <v>5.29140696294419</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>4.97876395234146</v>
+        <v>5.63425644521478</v>
       </c>
       <c r="G77" s="8" t="n">
-        <v>4.80390510422491</v>
+        <v>5.56182320666326</v>
       </c>
       <c r="H77" s="8" t="n">
-        <v>4.37797406542248</v>
+        <v>5.19044761884603</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18355,19 +18911,19 @@
         <v>25</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>2.78441054587726</v>
+        <v>2.77856644568533</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>3.06632121793268</v>
+        <v>3.01735106984763</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>3.151073931561</v>
+        <v>2.92921895256509</v>
       </c>
       <c r="G81" s="8" t="n">
-        <v>3.07655498134027</v>
+        <v>2.7376160189779</v>
       </c>
       <c r="H81" s="8" t="n">
-        <v>2.8767978784307</v>
+        <v>2.50077255017965</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18407,19 +18963,19 @@
         <v>25</v>
       </c>
       <c r="D83" s="8" t="n">
-        <v>-3.63304912443169</v>
+        <v>-3.5028728488479</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>-4.21787170091294</v>
+        <v>-3.71545644528728</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>-4.31069970952257</v>
+        <v>-3.43335223765334</v>
       </c>
       <c r="G83" s="8" t="n">
-        <v>-4.48826113980649</v>
+        <v>-3.39140407500577</v>
       </c>
       <c r="H83" s="8" t="n">
-        <v>-4.61870629715741</v>
+        <v>-3.4302074154828</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18511,19 +19067,19 @@
         <v>25</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.584196288966891</v>
+        <v>0.590886294703084</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>0.586384640174897</v>
+        <v>0.606396127800419</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>0.604191473129888</v>
+        <v>0.630644519692936</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>0.605887852613287</v>
+        <v>0.636905896692994</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>0.596688016379343</v>
+        <v>0.633111097718473</v>
       </c>
     </row>
   </sheetData>
@@ -18613,19 +19169,19 @@
         <v>25</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.940297910447761</v>
+        <v>0.958208358208955</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>0.907070303030303</v>
+        <v>0.913130909090909</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>0.82463768115942</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>0.65625</v>
+        <v>0.6525</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.465476190476191</v>
+        <v>0.461904761904762</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18639,19 +19195,19 @@
         <v>25</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>0.184804918429672</v>
+        <v>0.172486912161015</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>0.216090700452404</v>
+        <v>0.21192248620998</v>
       </c>
       <c r="F6" s="8" t="n">
         <v>0.277800866866406</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>0.408498600664463</v>
+        <v>0.410888755639463</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>0.578349703812881</v>
+        <v>0.58062604188431</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18665,19 +19221,19 @@
         <v>25</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>0.13553243193366</v>
+        <v>0.137996033187391</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>0.139395246116719</v>
+        <v>0.140228888965204</v>
       </c>
       <c r="F7" s="8" t="n">
         <v>0.136271326644928</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>0.115519399382813</v>
+        <v>0.114814655282813</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>0.0854877567380952</v>
+        <v>0.0848165718809524</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18691,19 +19247,19 @@
         <v>25</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>0.049272486496012</v>
+        <v>0.0344908789736239</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>0.0766954543356849</v>
+        <v>0.0716935972447758</v>
       </c>
       <c r="F8" s="8" t="n">
         <v>0.141529540221478</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>0.29297920128165</v>
+        <v>0.29607410035665</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>0.492861947074786</v>
+        <v>0.495809470003357</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18726,10 +19282,10 @@
         <v>0.502758732530204</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>0.516878794926939</v>
+        <v>0.516284617259001</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>0.527201158436087</v>
+        <v>0.526635274942813</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18752,10 +19308,10 @@
         <v>10.8199959837434</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>11.0447785955898</v>
+        <v>11.0353196566456</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>11.2091042030001</v>
+        <v>11.2000956897199</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18769,19 +19325,19 @@
         <v>25</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.895501175501442</v>
+        <v>0.90918973690843</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>0.8517028157434</v>
+        <v>0.903316395767151</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>0.825786802598526</v>
+        <v>0.899841069589126</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0.814849746666521</v>
+        <v>0.898450504702143</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.805753154854832</v>
+        <v>0.897227032352088</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18821,19 +19377,19 @@
         <v>25</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.940297910447761</v>
+        <v>0.958208358208955</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>0.907070303030303</v>
+        <v>0.913130909090909</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>0.829577464788732</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>0.6875</v>
+        <v>0.684090909090909</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0.568269230769231</v>
+        <v>0.565384615384615</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18847,19 +19403,19 @@
         <v>25</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>0.184804918429672</v>
+        <v>0.172486912161015</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>0.216090700452404</v>
+        <v>0.21192248620998</v>
       </c>
       <c r="F14" s="8" t="n">
         <v>0.275269342729324</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>0.388447069694966</v>
+        <v>0.390619937854057</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>0.503269330002712</v>
+        <v>0.505107910752712</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18873,19 +19429,19 @@
         <v>25</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>0.13553243193366</v>
+        <v>0.137996033187391</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>0.139395246116719</v>
+        <v>0.140228888965204</v>
       </c>
       <c r="F15" s="8" t="n">
         <v>0.137726550119718</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>0.122102341257102</v>
+        <v>0.121461664802557</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>0.105188526596154</v>
+        <v>0.10464641575</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18899,19 +19455,19 @@
         <v>25</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>0.049272486496012</v>
+        <v>0.0344908789736239</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>0.0766954543356849</v>
+        <v>0.0716935972447758</v>
       </c>
       <c r="F16" s="8" t="n">
         <v>0.137542792609606</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>0.266344728437864</v>
+        <v>0.2691582730515</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>0.398080803406558</v>
+        <v>0.400461495002712</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18934,10 +19490,10 @@
         <v>0.505245691848059</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>0.52362124887122</v>
+        <v>0.523081087354913</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>0.539478971874152</v>
+        <v>0.539021912129585</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18960,10 +19516,10 @@
         <v>10.8595868294008</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>11.1521142691348</v>
+        <v>11.1435152337309</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>11.4045593571509</v>
+        <v>11.3972832502707</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18977,19 +19533,19 @@
         <v>25</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.895501175501442</v>
+        <v>0.90918973690843</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>0.8517028157434</v>
+        <v>0.903316395767151</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>0.823933653229554</v>
+        <v>0.899592563058519</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>0.809863406060474</v>
+        <v>0.897774921343093</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0.796954471228903</v>
+        <v>0.896033196852186</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19029,19 +19585,19 @@
         <v>25</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.940297910447761</v>
+        <v>0.958208358208955</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>0.907070303030303</v>
+        <v>0.913130909090909</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>0.842857142857143</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>0.747706422018349</v>
+        <v>0.744954128440367</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0.686013986013986</v>
+        <v>0.683916083916084</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19055,19 +19611,19 @@
         <v>25</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>0.184804918429672</v>
+        <v>0.172486912161015</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>0.216090700452404</v>
+        <v>0.21192248620998</v>
       </c>
       <c r="F22" s="8" t="n">
         <v>0.268463816802364</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>0.349815679753734</v>
+        <v>0.35156992193722</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>0.417268174547427</v>
+        <v>0.41860532418379</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19081,19 +19637,19 @@
         <v>25</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>0.13553243193366</v>
+        <v>0.137996033187391</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>0.139395246116719</v>
+        <v>0.140228888965204</v>
       </c>
       <c r="F23" s="8" t="n">
         <v>0.141638644396104</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>0.134785073308486</v>
+        <v>0.13426782993234</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>0.127754862979021</v>
+        <v>0.127360600545455</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19107,19 +19663,19 @@
         <v>25</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>0.049272486496012</v>
+        <v>0.0344908789736239</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>0.0766954543356849</v>
+        <v>0.0716935972447758</v>
       </c>
       <c r="F24" s="8" t="n">
         <v>0.12682517240626</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>0.215030606445248</v>
+        <v>0.217302092004881</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>0.289513311568406</v>
+        <v>0.291244723638336</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19142,10 +19698,10 @@
         <v>0.511931413650602</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>0.536611297754696</v>
+        <v>0.536175204053458</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>0.553542649085028</v>
+        <v>0.55321024199807</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19168,10 +19724,10 @@
         <v>10.966019362532</v>
       </c>
       <c r="G26" s="8" t="n">
-        <v>11.358907768625</v>
+        <v>11.3519654281155</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>11.6284443519054</v>
+        <v>11.6231526378107</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19185,19 +19741,19 @@
         <v>25</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.895501175501442</v>
+        <v>0.90918973690843</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>0.8517028157434</v>
+        <v>0.903316395767151</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>0.818951810120757</v>
+        <v>0.898924500047668</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>0.800256694801117</v>
+        <v>0.896473338724741</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0.786875979075566</v>
+        <v>0.894665712552299</v>
       </c>
     </row>
   </sheetData>
@@ -20352,13 +20908,13 @@
         <v>79</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>0.76</v>
+        <v>0.891019087752599</v>
       </c>
       <c r="D13" s="0" t="n">
         <v>0.91130964597661</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>0.199091639442908</v>
+        <v>0.0227723047720441</v>
       </c>
       <c r="F13" s="0" t="n">
         <v>0.91130964597661</v>
@@ -20390,7 +20946,7 @@
         <v>79</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>0.76</v>
+        <v>0.891019087752599</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>87</v>
@@ -20399,7 +20955,7 @@
         <v>87</v>
       </c>
       <c r="F14" s="0" t="n">
-        <v>0.76</v>
+        <v>0.891019087752599</v>
       </c>
       <c r="G14" s="0" t="s">
         <v>88</v>
@@ -20504,7 +21060,7 @@
         <v>102</v>
       </c>
       <c r="C17" s="0" t="n">
-        <v>0.184804918429672</v>
+        <v>0.172486912161015</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>87</v>
@@ -20513,7 +21069,7 @@
         <v>87</v>
       </c>
       <c r="F17" s="0" t="n">
-        <v>0.184804918429672</v>
+        <v>0.172486912161015</v>
       </c>
       <c r="G17" s="0" t="s">
         <v>103</v>
@@ -20615,16 +21171,16 @@
         <v>102</v>
       </c>
       <c r="C20" s="0" t="n">
-        <v>1.326317431446</v>
+        <v>1.31399942517734</v>
       </c>
       <c r="D20" s="0" t="n">
         <v>1.3568</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>0.0229828605364608</v>
+        <v>0.0325727500351687</v>
       </c>
       <c r="F20" s="0" t="n">
-        <v>1.326317431446</v>
+        <v>1.31399942517734</v>
       </c>
       <c r="G20" s="0" t="s">
         <v>132</v>
@@ -20804,7 +21360,7 @@
         <v>95</v>
       </c>
       <c r="C26" s="0" t="n">
-        <v>0.933333333333333</v>
+        <v>0.953333333333333</v>
       </c>
       <c r="H26" s="0" t="s">
         <v>227</v>
@@ -20818,7 +21374,7 @@
         <v>102</v>
       </c>
       <c r="C27" s="0" t="n">
-        <v>1.32895604482763</v>
+        <v>1.31520093782763</v>
       </c>
       <c r="H27" s="0" t="s">
         <v>228</v>
@@ -20832,7 +21388,7 @@
         <v>79</v>
       </c>
       <c r="C28" s="0" t="n">
-        <v>1.020951750271</v>
+        <v>1.03162943469389</v>
       </c>
       <c r="H28" s="7" t="s">
         <v>160</v>
@@ -20893,13 +21449,13 @@
         <v>102</v>
       </c>
       <c r="C33" s="0" t="n">
-        <v>8.11382745599041</v>
+        <v>8.23237923794364</v>
       </c>
       <c r="D33" s="0" t="n">
         <v>8.24</v>
       </c>
       <c r="E33" s="0" t="n">
-        <v>0.0155503114521425</v>
+        <v>0.000925705903007446</v>
       </c>
       <c r="J33" s="7" t="s">
         <v>169</v>
@@ -20913,13 +21469,13 @@
         <v>102</v>
       </c>
       <c r="C34" s="0" t="n">
-        <v>1.326317431446</v>
+        <v>1.31399942517734</v>
       </c>
       <c r="D34" s="0" t="n">
         <v>1.3568</v>
       </c>
       <c r="E34" s="0" t="n">
-        <v>0.0229828605364608</v>
+        <v>0.0325727500351687</v>
       </c>
       <c r="J34" s="0" t="s">
         <v>229</v>
@@ -20953,13 +21509,13 @@
         <v>102</v>
       </c>
       <c r="C36" s="0" t="n">
-        <v>0.447442135437141</v>
+        <v>0.453979748267183</v>
       </c>
       <c r="D36" s="0" t="n">
         <v>0.4544</v>
       </c>
       <c r="E36" s="0" t="n">
-        <v>0.0155503114521423</v>
+        <v>0.000925705903007223</v>
       </c>
       <c r="J36" s="7" t="s">
         <v>175</v>
@@ -20973,13 +21529,13 @@
         <v>102</v>
       </c>
       <c r="C37" s="0" t="n">
-        <v>4.74006788910727</v>
+        <v>4.86440006449912</v>
       </c>
       <c r="D37" s="0" t="n">
         <v>4.832</v>
       </c>
       <c r="E37" s="0" t="n">
-        <v>0.0193946823217441</v>
+        <v>-0.00666064963191937</v>
       </c>
       <c r="J37" s="0" t="s">
         <v>230</v>
@@ -20993,13 +21549,13 @@
         <v>95</v>
       </c>
       <c r="C38" s="0" t="n">
-        <v>0.584196288966891</v>
+        <v>0.590886294703084</v>
       </c>
       <c r="D38" s="0" t="n">
         <v>0.586407766990291</v>
       </c>
       <c r="E38" s="0" t="n">
-        <v>-0.00221147802340016</v>
+        <v>0.00447852771279256</v>
       </c>
       <c r="J38" s="7" t="s">
         <v>179</v>
@@ -28124,22 +28680,22 @@
         <v>25</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>29.3181542946211</v>
+        <v>42.7024438874061</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>40.6837030341992</v>
+        <v>32.1474767393228</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>18.5333004436762</v>
+        <v>31.9865189051237</v>
       </c>
       <c r="F5" s="0" t="n">
-        <v>89.4072913196021</v>
+        <v>79.3186736969194</v>
       </c>
       <c r="G5" s="0" t="n">
-        <v>0</v>
+        <v>14.7158090153289</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>165.385125098764</v>
+        <v>151.832159599564</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28176,22 +28732,22 @@
         <v>25</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>59.3759198319985</v>
+        <v>92.3020751396992</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>22.4643124182484</v>
+        <v>14.0258577919704</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>38.0907432888378</v>
+        <v>62.5093886705524</v>
       </c>
       <c r="F7" s="0" t="n">
-        <v>64.0871592914773</v>
+        <v>54.0932091792606</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>23.0607724030104</v>
+        <v>40.7450520816997</v>
       </c>
       <c r="H7" s="0" t="n">
-        <v>127.998914422528</v>
+        <v>114.531356910427</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28228,22 +28784,22 @@
         <v>25</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>1.67596299946592</v>
+        <v>18.059783859417</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>73.6220207728507</v>
+        <v>65.2797933923325</v>
       </c>
       <c r="E9" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>131.441343167283</v>
+        <v>121.616519520606</v>
       </c>
       <c r="G9" s="0" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="0" t="n">
-        <v>223.347359908264</v>
+        <v>210.219669676205</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28384,22 +28940,22 @@
         <v>25</v>
       </c>
       <c r="C15" s="0" t="n">
-        <v>28.9478728721375</v>
+        <v>42.0547099034431</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>46.4587473501892</v>
+        <v>37.8138300287792</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>15.369612104278</v>
+        <v>29.2703536220292</v>
       </c>
       <c r="F15" s="0" t="n">
-        <v>107.886966936021</v>
+        <v>97.4799812272516</v>
       </c>
       <c r="G15" s="0" t="n">
-        <v>0</v>
+        <v>9.18148359729564</v>
       </c>
       <c r="H15" s="0" t="n">
-        <v>200.295601984497</v>
+        <v>186.004272962873</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28436,22 +28992,22 @@
         <v>25</v>
       </c>
       <c r="C17" s="0" t="n">
-        <v>23.1820369485176</v>
+        <v>35.2935964748211</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>45.2199002083101</v>
+        <v>37.0203110432463</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>22.7200316111757</v>
+        <v>25.4105274316058</v>
       </c>
       <c r="F17" s="0" t="n">
-        <v>94.3099634137179</v>
+        <v>84.6192305561052</v>
       </c>
       <c r="G17" s="0" t="n">
-        <v>0</v>
+        <v>6.97795763461624</v>
       </c>
       <c r="H17" s="0" t="n">
-        <v>171.098987787857</v>
+        <v>158.080593001818</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28482,33 +29038,33 @@
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B19" s="0" t="s">
         <v>25</v>
       </c>
       <c r="C19" s="0" t="n">
-        <v>23.8096044663599</v>
+        <v>35.4908489461709</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>44.6102152292373</v>
+        <v>36.893864334863</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>23.1511957531321</v>
+        <v>24.7620131596956</v>
       </c>
       <c r="F19" s="0" t="n">
-        <v>94.0446881769054</v>
+        <v>84.9273687459971</v>
       </c>
       <c r="G19" s="0" t="n">
-        <v>0</v>
+        <v>5.08921454128713</v>
       </c>
       <c r="H19" s="0" t="n">
-        <v>171.608975875627</v>
+        <v>159.365556775542</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B20" s="0" t="s">
         <v>24</v>
@@ -28534,33 +29090,33 @@
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B21" s="0" t="s">
         <v>25</v>
       </c>
       <c r="C21" s="0" t="n">
-        <v>42.0533986767359</v>
+        <v>77.4655715771412</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>32.1764443362143</v>
+        <v>22.3698845877318</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>31.3999379112654</v>
+        <v>47.3463361505384</v>
       </c>
       <c r="F21" s="0" t="n">
-        <v>79.3598252645416</v>
+        <v>67.7647255965987</v>
       </c>
       <c r="G21" s="0" t="n">
-        <v>14.0953236265844</v>
+        <v>34.5469939353261</v>
       </c>
       <c r="H21" s="0" t="n">
-        <v>151.900412765808</v>
+        <v>136.313293858722</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B22" s="0" t="s">
         <v>24</v>
@@ -28586,33 +29142,33 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B23" s="0" t="s">
         <v>25</v>
       </c>
       <c r="C23" s="0" t="n">
-        <v>66.2968296952018</v>
+        <v>111.220230326159</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>24.97815859716</v>
+        <v>14.0372460574747</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>42.1485558476493</v>
+        <v>83.3903430416069</v>
       </c>
       <c r="F23" s="0" t="n">
-        <v>70.858320897079</v>
+        <v>57.9182437663935</v>
       </c>
       <c r="G23" s="0" t="n">
-        <v>28.6920480373452</v>
+        <v>56.438979740397</v>
       </c>
       <c r="H23" s="0" t="n">
-        <v>140.490522982048</v>
+        <v>123.087814949879</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B24" s="0" t="s">
         <v>24</v>
@@ -28638,33 +29194,33 @@
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B25" s="0" t="s">
         <v>25</v>
       </c>
       <c r="C25" s="0" t="n">
-        <v>38.97521417996</v>
+        <v>62.5915194246029</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>34.1396376674474</v>
+        <v>26.0394168195137</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>28.4090792775149</v>
+        <v>41.0211442583833</v>
       </c>
       <c r="F25" s="0" t="n">
-        <v>81.6784466841414</v>
+        <v>72.1009244164661</v>
       </c>
       <c r="G25" s="0" t="n">
-        <v>10.1143910898168</v>
+        <v>27.104298804064</v>
       </c>
       <c r="H25" s="0" t="n">
-        <v>155.01223779137</v>
+        <v>142.137530278866</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>24</v>
@@ -28690,33 +29246,33 @@
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B27" s="0" t="s">
         <v>25</v>
       </c>
       <c r="C27" s="0" t="n">
-        <v>55.6569346462762</v>
+        <v>87.3469608861259</v>
       </c>
       <c r="D27" s="0" t="n">
-        <v>27.595701654582</v>
+        <v>19.9314473620382</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>38.0900247122983</v>
+        <v>55.2254221299056</v>
       </c>
       <c r="F27" s="0" t="n">
-        <v>73.9497587226922</v>
+        <v>64.8832822881803</v>
       </c>
       <c r="G27" s="0" t="n">
-        <v>23.3841530582107</v>
+        <v>39.492760411572</v>
       </c>
       <c r="H27" s="0" t="n">
-        <v>144.639550975324</v>
+        <v>132.443033803293</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B28" s="0" t="s">
         <v>24</v>
@@ -28742,33 +29298,33 @@
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B29" s="0" t="s">
         <v>25</v>
       </c>
       <c r="C29" s="0" t="n">
-        <v>19.631852075254</v>
+        <v>41.179051772666</v>
       </c>
       <c r="D29" s="0" t="n">
-        <v>48.536489397631</v>
+        <v>33.1945742459464</v>
       </c>
       <c r="E29" s="0" t="n">
-        <v>17.2508451615994</v>
+        <v>30.7186467148996</v>
       </c>
       <c r="F29" s="0" t="n">
-        <v>97.2318261128388</v>
+        <v>80.3721989270524</v>
       </c>
       <c r="G29" s="0" t="n">
-        <v>0</v>
+        <v>13.4307715992821</v>
       </c>
       <c r="H29" s="0" t="n">
-        <v>173.286743179448</v>
+        <v>152.896179222392</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B30" s="0" t="s">
         <v>24</v>
@@ -28794,33 +29350,33 @@
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B31" s="0" t="s">
         <v>25</v>
       </c>
       <c r="C31" s="0" t="n">
-        <v>53.1327148381051</v>
+        <v>96.6819274244893</v>
       </c>
       <c r="D31" s="0" t="n">
-        <v>28.2500900726785</v>
+        <v>17.627861750111</v>
       </c>
       <c r="E31" s="0" t="n">
-        <v>37.1431840028499</v>
+        <v>65.3203249900644</v>
       </c>
       <c r="F31" s="0" t="n">
-        <v>74.722621323387</v>
+        <v>62.1611897455478</v>
       </c>
       <c r="G31" s="0" t="n">
-        <v>22.0571784879102</v>
+        <v>44.2043706037556</v>
       </c>
       <c r="H31" s="0" t="n">
-        <v>145.676811875061</v>
+        <v>128.786806740496</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B32" s="0" t="s">
         <v>24</v>
@@ -28846,33 +29402,33 @@
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B33" s="0" t="s">
         <v>25</v>
       </c>
       <c r="C33" s="0" t="n">
-        <v>79.956061333637</v>
+        <v>111.348690873544</v>
       </c>
       <c r="D33" s="0" t="n">
-        <v>21.6126400917217</v>
+        <v>14.0055131921113</v>
       </c>
       <c r="E33" s="0" t="n">
-        <v>48.5839857186112</v>
+        <v>83.5509689015889</v>
       </c>
       <c r="F33" s="0" t="n">
-        <v>66.8834898550481</v>
+        <v>57.8807457838855</v>
       </c>
       <c r="G33" s="0" t="n">
-        <v>35.5167399162536</v>
+        <v>56.5981321400752</v>
       </c>
       <c r="H33" s="0" t="n">
-        <v>135.155887210051</v>
+        <v>123.037448819176</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B34" s="0" t="s">
         <v>24</v>
@@ -28898,33 +29454,33 @@
     </row>
     <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B35" s="0" t="s">
         <v>25</v>
       </c>
       <c r="C35" s="0" t="n">
-        <v>28.6686491093053</v>
+        <v>41.5861840850245</v>
       </c>
       <c r="D35" s="0" t="n">
-        <v>41.1626167560806</v>
+        <v>32.8703154331618</v>
       </c>
       <c r="E35" s="0" t="n">
-        <v>17.9048503109729</v>
+        <v>31.0316851695497</v>
       </c>
       <c r="F35" s="0" t="n">
-        <v>89.9288782526563</v>
+        <v>80.1059286040378</v>
       </c>
       <c r="G35" s="0" t="n">
-        <v>0</v>
+        <v>13.5936691564894</v>
       </c>
       <c r="H35" s="0" t="n">
-        <v>166.000617705248</v>
+        <v>152.761170776291</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B36" s="0" t="s">
         <v>24</v>
@@ -28950,33 +29506,33 @@
     </row>
     <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B37" s="0" t="s">
         <v>25</v>
       </c>
       <c r="C37" s="0" t="n">
-        <v>37.9888188051891</v>
+        <v>65.9733081614755</v>
       </c>
       <c r="D37" s="0" t="n">
-        <v>26.3693826516689</v>
+        <v>17.8331563567926</v>
       </c>
       <c r="E37" s="0" t="n">
-        <v>30.0075470835581</v>
+        <v>43.4499265011462</v>
       </c>
       <c r="F37" s="0" t="n">
-        <v>64.8648455996717</v>
+        <v>54.7762279769889</v>
       </c>
       <c r="G37" s="0" t="n">
-        <v>15.4568152853614</v>
+        <v>33.2193083376806</v>
       </c>
       <c r="H37" s="0" t="n">
-        <v>124.164802758546</v>
+        <v>110.611837259347</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B38" s="0" t="s">
         <v>24</v>
@@ -29002,28 +29558,28 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B39" s="0" t="s">
         <v>25</v>
       </c>
       <c r="C39" s="0" t="n">
-        <v>37.272159199947</v>
+        <v>63.1152778628983</v>
       </c>
       <c r="D39" s="0" t="n">
-        <v>26.8482963735504</v>
+        <v>18.5559950506315</v>
       </c>
       <c r="E39" s="0" t="n">
-        <v>29.3753820814155</v>
+        <v>42.2898876657917</v>
       </c>
       <c r="F39" s="0" t="n">
-        <v>65.3864325327258</v>
+        <v>55.5634828841074</v>
       </c>
       <c r="G39" s="0" t="n">
-        <v>14.7138236052813</v>
+        <v>32.0971684788411</v>
       </c>
       <c r="H39" s="0" t="n">
-        <v>124.78029536503</v>
+        <v>111.540848436073</v>
       </c>
     </row>
   </sheetData>
@@ -29042,37 +29598,37 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="20.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>240</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B4" s="10" t="n">
-        <v>3.85958443326141</v>
+        <v>0.278462448717743</v>
       </c>
       <c r="C4" s="10" t="n">
-        <v>6.83574980535934</v>
+        <v>0.998737622652914</v>
       </c>
       <c r="D4" s="10" t="n">
         <v>0</v>
@@ -29080,13 +29636,13 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B5" s="10" t="n">
-        <v>-5.88534447757876</v>
+        <v>3.92705419242967</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>-11.1413968293039</v>
+        <v>6.83574981687241</v>
       </c>
       <c r="D5" s="10" t="n">
         <v>0</v>
@@ -29094,13 +29650,13 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B6" s="10" t="n">
-        <v>12.9049982604497</v>
+        <v>-5.95678697517301</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>9.54429154017814</v>
+        <v>-11.080980203771</v>
       </c>
       <c r="D6" s="10" t="n">
         <v>0</v>
@@ -29108,103 +29664,103 @@
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B7" s="10" t="n">
-        <v>0</v>
+        <v>11.9280878155531</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>0</v>
+        <v>8.28314072725259</v>
       </c>
       <c r="D7" s="10" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>310</v>
+    <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>315</v>
       </c>
       <c r="B8" s="10" t="n">
-        <f aca="false">SUM(B4:B7)</f>
-        <v>10.8792382161324</v>
+        <v>14.0867103273899</v>
       </c>
       <c r="C8" s="10" t="n">
-        <f aca="false">SUM(C4:C7)</f>
-        <v>5.23864451623356</v>
+        <v>13.6552150146742</v>
       </c>
       <c r="D8" s="10" t="n">
-        <f aca="false">SUM(D4:D7)</f>
+        <v>14.7158090153289</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="B9" s="10" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="B9" s="10" t="n">
-        <v>10.8792382161324</v>
-      </c>
       <c r="C9" s="10" t="n">
-        <v>5.23864451623356</v>
+        <v>0</v>
       </c>
       <c r="D9" s="10" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="B10" s="0" t="str">
-        <f aca="false">IF(ABS(B8-B9)&lt;0.01,"通過","不通過")</f>
+        <v>317</v>
+      </c>
+      <c r="B10" s="10" t="n">
+        <f aca="false">SUM(B4:B9)</f>
+        <v>24.2635278089173</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <f aca="false">SUM(C4:C9)</f>
+        <v>18.6918629776811</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <f aca="false">SUM(D4:D9)</f>
+        <v>14.7158090153289</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>24.2635278089173</v>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>18.6918629776811</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>14.7158090153289</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="B12" s="0" t="str">
+        <f aca="false">IF(ABS(B10-B11)&lt;0.01,"通過","不通過")</f>
         <v>通過</v>
       </c>
-      <c r="C10" s="0" t="str">
-        <f aca="false">IF(ABS(C8-C9)&lt;0.01,"通過","不通過")</f>
+      <c r="C12" s="0" t="str">
+        <f aca="false">IF(ABS(C10-C11)&lt;0.01,"通過","不通過")</f>
         <v>通過</v>
       </c>
-      <c r="D10" s="0" t="str">
-        <f aca="false">IF(ABS(D8-D9)&lt;0.01,"通過","不通過")</f>
+      <c r="D12" s="0" t="str">
+        <f aca="false">IF(ABS(D10-D11)&lt;0.01,"通過","不通過")</f>
         <v>通過</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>313</v>
-      </c>
-      <c r="B12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>314</v>
-      </c>
-      <c r="B13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="10" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B14" s="10" t="n">
-        <v>-2.02576004431734</v>
+        <v>0</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>-4.30564702394458</v>
+        <v>0</v>
       </c>
       <c r="D14" s="10" t="n">
         <v>0</v>
@@ -29212,16 +29768,44 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B15" s="10" t="n">
-        <v>12.9049982604497</v>
+        <v>0.278462448717743</v>
       </c>
       <c r="C15" s="10" t="n">
-        <v>9.54429154017814</v>
+        <v>0.998737622652914</v>
       </c>
       <c r="D15" s="10" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>322</v>
+      </c>
+      <c r="B16" s="10" t="n">
+        <v>9.89835503280972</v>
+      </c>
+      <c r="C16" s="10" t="n">
+        <v>4.03791034035401</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>323</v>
+      </c>
+      <c r="B17" s="10" t="n">
+        <v>14.0867103273899</v>
+      </c>
+      <c r="C17" s="10" t="n">
+        <v>13.6552150146742</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>14.7158090153289</v>
       </c>
     </row>
   </sheetData>
